--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/일별투자수익_2026-08-01_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/일별투자수익_2026-08-01_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>26810473</v>
+        <v>26830038</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>26800514</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9948</v>
+        <v>29513</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.04</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0445</v>
+        <v>0.1321</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>27018798</v>
+        <v>27037934</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>27008184</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>10605</v>
+        <v>29741</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0478</v>
+        <v>0.1339</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>27035529</v>
+        <v>27054061</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>27024300</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11227</v>
+        <v>29759</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>2.96</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0513</v>
+        <v>0.1359</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>26950208</v>
+        <v>26967958</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>26938289</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11914</v>
+        <v>29664</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>2.92</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0552</v>
+        <v>0.1375</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>26667987</v>
+        <v>26685069</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>26655718</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12271</v>
+        <v>29353</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>2.91</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0578</v>
+        <v>0.1382</v>
       </c>
     </row>
     <row r="9">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>26191469</v>
+        <v>26208004</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>26179169</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12293</v>
+        <v>28828</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>2.9</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.059</v>
+        <v>0.1384</v>
       </c>
     </row>
     <row r="10">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>25557858</v>
+        <v>25574091</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>25545958</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11898</v>
+        <v>28131</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>2.92</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0582</v>
+        <v>0.1377</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>24997883</v>
+        <v>25014050</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>24986538</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>11348</v>
+        <v>27515</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>2.94</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.0564</v>
+        <v>0.1367</v>
       </c>
     </row>
     <row r="12">
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>24900027</v>
+        <v>24916556</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>24889141</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10879</v>
+        <v>27408</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>2.95</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.0541</v>
+        <v>0.1363</v>
       </c>
     </row>
     <row r="13">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>25021546</v>
+        <v>25038904</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>25011361</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>10184</v>
+        <v>27542</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>2.98</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.0499</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="14">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>25340702</v>
+        <v>25359026</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>25331129</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9570</v>
+        <v>27894</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>3.02</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.0457</v>
+        <v>0.1331</v>
       </c>
     </row>
     <row r="15">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>25727823</v>
+        <v>25747154</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>25718836</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8990</v>
+        <v>28321</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>3.07</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.0416</v>
+        <v>0.1309</v>
       </c>
     </row>
     <row r="16">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>25975401</v>
+        <v>25995399</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>25966805</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>8596</v>
+        <v>28594</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>3.11</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.0389</v>
+        <v>0.1294</v>
       </c>
     </row>
     <row r="17">
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>26048283</v>
+        <v>26068550</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>26039881</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>8408</v>
+        <v>28675</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>3.13</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.0377</v>
+        <v>0.1285</v>
       </c>
     </row>
     <row r="18">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>25993163</v>
+        <v>26013183</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>25984567</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>8594</v>
+        <v>28614</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0387</v>
+        <v>0.1289</v>
       </c>
     </row>
     <row r="19">
@@ -859,19 +859,19 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>26249357</v>
+        <v>26268936</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>26240030</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>9316</v>
+        <v>28895</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>3.07</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.0423</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="20">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>26504842</v>
+        <v>26524007</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>26494834</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>10011</v>
+        <v>29176</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>3.01</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.0458</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="21">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>26723567</v>
+        <v>26742349</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>26712931</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>10634</v>
+        <v>29416</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>2.98</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0487</v>
+        <v>0.1347</v>
       </c>
     </row>
     <row r="22">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>26756203</v>
+        <v>26774845</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>26745390</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>10810</v>
+        <v>29452</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>2.99</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.0494</v>
+        <v>0.1345</v>
       </c>
     </row>
     <row r="23">
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>26478274</v>
+        <v>26496857</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>26467707</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>10563</v>
+        <v>29146</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>3.01</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="24">
@@ -969,19 +969,19 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>25951644</v>
+        <v>25970340</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>25941773</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>9871</v>
+        <v>28567</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>3.06</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.0454</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="25">
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>25375330</v>
+        <v>25394136</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>25366208</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>9127</v>
+        <v>27933</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.0424</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="26">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>25188289</v>
+        <v>25207385</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>25179655</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8632</v>
+        <v>27728</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="27">
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>25281449</v>
+        <v>25301031</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>25273193</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8249</v>
+        <v>27831</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.1287</v>
       </c>
     </row>
     <row r="28">
@@ -1057,19 +1057,19 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>25602105</v>
+        <v>25622093</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>25593903</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8196</v>
+        <v>28184</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>3.13</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.0374</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="29">
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>26102548</v>
+        <v>26122944</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>26094204</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8339</v>
+        <v>28735</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.0373</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="30">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>26530746</v>
+        <v>26551191</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>26521983</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8761</v>
+        <v>29206</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>3.11</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.0388</v>
+        <v>0.1294</v>
       </c>
     </row>
     <row r="31">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>702981504</v>
+        <v>703486091</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>702712201</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>269234</v>
+        <v>773821</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>3.03</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>0.0462</v>
+        <v>0.1327</v>
       </c>
     </row>
   </sheetData>
